--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_monthly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,101 +916,105 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.684634074996662</v>
+        <v>2.628439928980015</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3416882532303288</v>
+        <v>-0.7764411386548676</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4131976008746485</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08522410333287994</v>
+        <v>0.1304446614088351</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1645222726818187</v>
+        <v>0.1254409353393415</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9096847486509514</v>
+        <v>0.8219255893212155</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.08846498007124048</v>
+        <v>0.04720025504048997</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3877545076850768</v>
+        <v>0.2004899471564507</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5454410266003107</v>
+        <v>0.2730536751796479</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.2362358235613322</v>
+        <v>0.1142316773877133</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.8708733918691299</v>
+        <v>1.610428448490837</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.2242450684898891</v>
+        <v>-0.7365581124409895</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,51 +1063,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.628439928980015</v>
+        <v>11.86787265887571</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.7764411386548676</v>
+        <v>-0.2071724995152153</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4131976008746485</v>
+        <v>-0.4380050570761583</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1304446614088351</v>
+        <v>0.1299733964084162</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1254409353393415</v>
+        <v>0.1778923730530282</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8219255893212155</v>
+        <v>0.9139449020164726</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.04720025504048997</v>
+        <v>0.09573117744529203</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2004899471564507</v>
+        <v>0.3960094515501504</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2730536751796479</v>
+        <v>0.5538463576083222</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.1142316773877133</v>
+        <v>0.2185618085880838</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.610428448490837</v>
+        <v>1.924141575557356</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
@@ -1115,15 +1119,15 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.7365581124409895</v>
+        <v>-0.06573162888874362</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
@@ -1143,11 +1147,11 @@
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,140 +1187,116 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11.86787265887571</v>
+        <v>5.923382388083009</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2071724995152153</v>
+        <v>-0.5734300378036365</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4380050570761583</v>
+        <v>-0.609877450557176</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1299733964084162</v>
+        <v>0.2684392248639847</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1778923730530282</v>
+        <v>0.1434113035652138</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9139449020164726</v>
+        <v>0.9507242260721386</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09573117744529203</v>
+        <v>0.07169457745996621</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.3960094515501504</v>
+        <v>0.3365826559752773</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5538463576083222</v>
+        <v>0.4671466533676559</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2185618085880838</v>
+        <v>0.1175557112243894</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.924141575557356</v>
+        <v>3.682584690591698</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.06573162888874362</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0.204334427230231</v>
-      </c>
+        <v>-0.4973297173691631</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
           <t>0/6</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.923382388083009</v>
+        <v>13.81239757140091</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5734300378036365</v>
+        <v>-0.0873645975490448</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.609877450557176</v>
+        <v>-0.5543499163256077</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2684392248639847</v>
+        <v>0.2032017015674233</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1434113035652138</v>
+        <v>0.1826705696036831</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9507242260721386</v>
+        <v>0.9216131780744107</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.07169457745996621</v>
+        <v>0.1012632988027937</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3365826559752773</v>
+        <v>0.4132238299687809</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4671466533676559</v>
+        <v>0.5800727597840086</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.1175557112243894</v>
+        <v>0.1826703600390098</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>3.682584690591698</v>
+        <v>3.449946282588622</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,23 +1393,23 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.4973297173691631</v>
+        <v>0.07545006996472514</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
@@ -1441,11 +1421,11 @@
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,92 +1461,86 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13.81239757140091</v>
+        <v>5.235864334716949</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.0873645975490448</v>
+        <v>-0.6157900482139357</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5543499163256077</v>
+        <v>-0.2090256659061214</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2032017015674233</v>
+        <v>0.08206384573127987</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1826705696036831</v>
+        <v>0.1073704007440577</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9216131780744107</v>
+        <v>0.8936381709741551</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.1012632988027937</v>
+        <v>0.06769105941143061</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.4132238299687809</v>
+        <v>0.4147376100602873</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5800727597840086</v>
+        <v>0.5752930939110084</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.1826703600390098</v>
+        <v>0.3238408982839091</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>3.449946282588622</v>
+        <v>3.847068823288041</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.07545006996472514</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.386327081248736</v>
-      </c>
+        <v>-0.5472467773880032</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
         <v>0.5</v>
       </c>
@@ -1576,45 +1550,27 @@
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,79 +1611,79 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.235864334716949</v>
+        <v>14.00878731516505</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.6157900482139357</v>
+        <v>-0.07526444752448169</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2090256659061214</v>
+        <v>-0.4671232695897851</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08206384573127987</v>
+        <v>0.1425280209701915</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1073704007440577</v>
+        <v>0.1747286212623221</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8936381709741551</v>
+        <v>0.9163589889236012</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.06769105941143061</v>
+        <v>0.1017824910786225</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.4147376100602873</v>
+        <v>0.4347039636642429</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5752930939110084</v>
+        <v>0.6107191864778968</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.3238408982839091</v>
+        <v>0.2178921447608574</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>3.847068823288041</v>
+        <v>3.486808642003445</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.5472467773880032</v>
+        <v>0.08970889353824885</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1739,11 +1695,11 @@
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>14.00878731516505</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.07526444752448169</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4671232695897851</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1425280209701915</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1747286212623221</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9163589889236012</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.1017824910786225</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.4347039636642429</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.6107191864778968</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.2178921447608574</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>3.486808642003445</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.08970889353824885</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.4047076586635221</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4662306966820124</v>
+        <v>0.1456635683267122</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.6173412189194043</v>
+        <v>0.2637362703305421</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.09188574888245429</v>
+        <v>0.1180176287204635</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1488918445234894</v>
+        <v>0.09464838563953046</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9418282548476454</v>
+        <v>0.9722991689750693</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1630913374762594</v>
+        <v>-0.135721852795745</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5804411953817679</v>
+        <v>0.6321264784029936</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3466644120689842</v>
+        <v>0.2884882608262321</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7519602345380432</v>
+        <v>0.3255727592241868</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.02334792565864707</v>
+        <v>-0.2257118017182801</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.056140469786753</v>
+        <v>0.4572722746277164</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.06754810166434866</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.7149673183492742</v>
+        <v>0.3400180353268318</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.7458483602049297</v>
+        <v>0.802942965732178</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01768827268138606</v>
+        <v>-0.2567607180060474</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1456635683267122</v>
+        <v>0.1019117619885797</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2637362703305421</v>
+        <v>0.2154753793582211</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.4380050570761586</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1180176287204635</v>
+        <v>0.209955706117895</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09464838563953046</v>
+        <v>0.1577159972003161</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9811634349030471</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.135721852795745</v>
+        <v>-0.3910419629857261</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.6321264784029936</v>
+        <v>0.1499730030920461</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2884882608262321</v>
+        <v>0.831192718696548</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.4380050570761586</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3255727592241868</v>
+        <v>0.8095036028939888</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2257118017182801</v>
+        <v>0.05695992522437687</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.4572722746277164</v>
+        <v>1.136961073453244</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06754810166434866</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.3400180353268318</v>
+        <v>0.288844016014292</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.802942965732178</v>
+        <v>0.2703278600904964</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2567607180060474</v>
+        <v>0.01457588745827887</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1019117619885797</v>
+        <v>-0.3197093201867722</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2154753793582211</v>
+        <v>-0.2495981977471486</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.6098774505571757</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.209955706117895</v>
+        <v>0.4349106047534014</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1577159972003161</v>
+        <v>0.161933865159753</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9811634349030471</v>
+        <v>0.9988919667590028</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3910419629857261</v>
+        <v>-0.5564315251194953</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1499730030920461</v>
+        <v>-0.1623531669993604</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.831192718696548</v>
+        <v>1.182742201377048</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.595666574932973</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.8095036028939888</v>
+        <v>0.5336768015276447</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.05695992522437687</v>
+        <v>-0.104154910292273</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.136961073453244</v>
+        <v>0.7495578116919465</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.1420856921406376</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.288844016014292</v>
+        <v>-0.2043023751327736</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2703278600904964</v>
+        <v>-0.07468600913571855</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.01457588745827887</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.2484731328554665</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.2723721664226417</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.03284513382298249</v>
-      </c>
+        <v>-0.1400782515738124</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,23 +2442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.3197093201867722</v>
+        <v>-0.1719997770634127</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2495981977471486</v>
+        <v>-0.08666562986286497</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.4349106047534014</v>
+        <v>0.3526760396798082</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.161933865159753</v>
+        <v>0.1723863215905274</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -2678,37 +2467,37 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5564315251194953</v>
+        <v>-0.5277315235233264</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1623531669993604</v>
+        <v>-0.1081552994646565</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.182742201377048</v>
+        <v>1.121737924058131</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.595666574932973</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5336768015276447</v>
+        <v>0.7532405065733498</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.104154910292273</v>
+        <v>0.02409575298131195</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7495578116919465</v>
+        <v>1.057938632836764</v>
       </c>
       <c r="X7" s="2" t="n">
         <v>-0.1420856921406376</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2043023751327736</v>
+        <v>-0.03153485659827238</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.07468600913571855</v>
+        <v>-0.01481585487843839</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1400782515738124</v>
+        <v>-0.01697043319527958</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,91 +2531,85 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1719997770634127</v>
+        <v>0.2925695514340041</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08666562986286497</v>
+        <v>0.4257824628723899</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3526760396798082</v>
+        <v>0.09955264025319233</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1723863215905274</v>
+        <v>0.09507811762339856</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9224376731301939</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5277315235233264</v>
+        <v>-0.1379451935448507</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1081552994646565</v>
+        <v>0.6279278609569019</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.121737924058131</v>
+        <v>0.293214159365938</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7532405065733498</v>
+        <v>0.4994053066639372</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.02409575298131195</v>
+        <v>-0.1241734372465926</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.057938632836764</v>
+        <v>0.7014229356397752</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1420856921406376</v>
+        <v>-0.08307751008271946</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03153485659827238</v>
+        <v>0.5118456750489424</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.01481585487843839</v>
+        <v>0.798304925794465</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.01697043319527958</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.4352865310961641</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.4356989028497757</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.0007307654649160167</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>-0.159294036643407</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.08270819824638442</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.06916594252835273</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2836,7 +2619,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,62 +2650,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2925695514340041</v>
+        <v>0.155136892308279</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.4257824628723899</v>
+        <v>0.274185920164117</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1911504799548355</v>
+        <v>-0.4341707534324699</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09955264025319233</v>
+        <v>0.2020371883620518</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.09507811762339856</v>
+        <v>0.154911528137777</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9224376731301939</v>
+        <v>0.9822714681440443</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1379451935448507</v>
+        <v>-0.3466732867683084</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.6279278609569019</v>
+        <v>0.233760024087988</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.293214159365938</v>
+        <v>0.7368833501353319</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1911504799548355</v>
+        <v>-0.4341707534324699</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4994053066639372</v>
+        <v>0.7680845875632039</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1241734372465926</v>
+        <v>0.0327664175259792</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7014229356397752</v>
+        <v>1.0787873877976</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08307751008271946</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.5118456750489424</v>
+        <v>0.3510984478848871</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.798304925794465</v>
+        <v>0.3628839347104611</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.159294036643407</v>
+        <v>-0.008647461845735283</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -2931,122 +2714,6 @@
         <v>0.08270819824638442</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.06916594252835273</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.155136892308279</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.274185920164117</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4341707534324699</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.2020371883620518</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.154911528137777</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9822714681440443</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3466732867683084</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.233760024087988</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7368833501353319</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.4341707534324699</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.7680845875632039</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.0327664175259792</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.0787873877976</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1144491365988818</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.3510984478848871</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3628839347104611</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.008647461845735283</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.212172480822915</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.2193572100669245</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.009203606741343906</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.08270819824638442</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.1361240023967677</v>
       </c>
     </row>
@@ -3061,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3446,7 +3113,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3456,7 +3123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3467,74 +3134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4214855010465173</v>
+        <v>0.1456481924702164</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.3487784252242632</v>
+        <v>0.08704982482296564</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1200249121443981</v>
+        <v>0.02913535421699465</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.200292846208758</v>
+        <v>0.07336880208048525</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.3379360465116279</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.272011052419783</v>
+        <v>0.1207562771902446</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.07033511810930126</v>
+        <v>-0.4720162998148467</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.132982746142185</v>
+        <v>0.1075578535930514</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1172230559518105</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1315697779645968</v>
+        <v>-0.08800978284713346</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.112279471679261</v>
+        <v>0.8172807306068304</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.01734303902616463</v>
+        <v>-0.4981566679308087</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1068371958786292</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3544,7 +3219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3575,62 +3250,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1456481924702164</v>
+        <v>0.309825691595069</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.08704982482296564</v>
+        <v>0.2428298651848617</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02913535421699465</v>
+        <v>0.1208509365587099</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07336880208048525</v>
+        <v>0.2020934073527834</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3379360465116279</v>
+        <v>0.9382267441860465</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>0.2601459135591284</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>0.7434803069533858</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1207562771902446</v>
+        <v>1.093541190435257</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4720162998148467</v>
+        <v>-0.01374130423147568</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1075578535930514</v>
+        <v>0.9740192890635779</v>
       </c>
       <c r="X5" s="2" t="n">
         <v>-0.1227419066313019</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.08800978284713346</v>
+        <v>0.04268328162290125</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8172807306068304</v>
+        <v>0.112279471679261</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4981566679308087</v>
+        <v>-0.0625707763457034</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3639,7 +3314,7 @@
         <v>0.1461342146462365</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1068371958786292</v>
+        <v>-0.007149815379016156</v>
       </c>
     </row>
     <row r="6">
@@ -3650,7 +3325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3668,95 +3343,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.309825691595069</v>
+        <v>0.4050864704605563</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2428298651848617</v>
+        <v>0.3332181830461667</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1208509365587099</v>
+        <v>0.08273142359005452</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2020934073527834</v>
+        <v>0.1180962070563869</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9382267441860465</v>
+        <v>0.9345930232558139</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.1729422453751833</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>0.6658069850939825</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>0.343473817797331</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2019757611901184</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.093541190435257</v>
+        <v>0.6988976436088852</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01374130423147568</v>
+        <v>-0.1996562657161938</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9740192890635779</v>
+        <v>0.6225095057326417</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.122741906631302</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.04268328162290125</v>
+        <v>0.1185153729880222</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.112279471679261</v>
+        <v>0.4703399767942977</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.0625707763457034</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.07855149375019499</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.07855149375019499</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.007149815379016156</v>
-      </c>
+        <v>-0.2392811250179974</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3766,7 +3427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3797,62 +3458,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4050864704605563</v>
+        <v>0.4342011775436574</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3332181830461667</v>
+        <v>0.3608437119323213</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2161164061045036</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.08273142359005452</v>
+        <v>0.1197392093328651</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1180962070563869</v>
+        <v>0.2064344599986419</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9345930232558139</v>
+        <v>0.9244186046511628</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1729422453751833</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.6658069850939825</v>
+        <v>0.2870819453199265</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.343473817797331</v>
+        <v>0.7169197413667834</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2019757611901184</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.6988976436088852</v>
+        <v>1.244361020252491</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1996562657161938</v>
+        <v>0.05730930099719478</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6225095057326417</v>
+        <v>1.108354808109552</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.122741906631302</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1185153729880222</v>
+        <v>0.1416920586490957</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4703399767942977</v>
+        <v>0.1360548097997625</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2392811250179974</v>
+        <v>0.004962127531792815</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3868,7 +3529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3886,89 +3547,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4342011775436574</v>
+        <v>0.2182581518238311</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3608437119323213</v>
+        <v>0.1559458821942616</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1197392093328651</v>
+        <v>0.07146802938810665</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2064344599986419</v>
+        <v>0.1071587332980531</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3609757233342479</v>
+        <v>-0.09542945485596188</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2870819453199265</v>
+        <v>0.8219283045048862</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7169197413667834</v>
+        <v>0.1895287014377966</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.1194163443509543</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.244361020252491</v>
+        <v>0.3467806998179932</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.05730930099719478</v>
+        <v>-0.3655371183728369</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.108354808109552</v>
+        <v>0.3088782513654108</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.1366025849960363</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1416920586490957</v>
+        <v>-0.03020881651768559</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1360548097997625</v>
+        <v>0.6081419065579503</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.004962127531792815</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.008945343788437254</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.02137532762751326</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.01216984932262721</v>
-      </c>
+        <v>-0.396949249610661</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3980,7 +3631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4011,180 +3662,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2182581518238311</v>
+        <v>0.4103901676897292</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1559458821942616</v>
+        <v>0.3382506032793406</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1616586033180829</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07146802938810665</v>
+        <v>0.124023134579484</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1071587332980531</v>
+        <v>0.2048556913882314</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.9273255813953488</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.09542945485596188</v>
+        <v>-0.3723569839339401</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.8219283045048862</v>
+        <v>0.2641585360415228</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1895287014377966</v>
+        <v>0.7395236171349165</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1194163443509543</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3467806998179932</v>
+        <v>1.247121582790439</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3655371183728369</v>
+        <v>0.05860979072278649</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3088782513654108</v>
+        <v>1.110813646591491</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1366025849960363</v>
+        <v>-0.122741906631302</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03020881651768559</v>
+        <v>0.1227373671565088</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.6081419065579503</v>
+        <v>0.1158212501088403</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.396949249610661</v>
+        <v>0.006198230269403471</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4103901676897292</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.3382506032793406</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3799797244656153</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.124023134579484</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2048556913882314</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9273255813953488</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3723569839339401</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.2641585360415228</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7395236171349165</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3799797244656153</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.247121582790439</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.05860979072278649</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.110813646591491</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.122741906631302</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.1227373671565088</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1158212501088403</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0.006198230269403471</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.00780544954459228</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.003184252267312004</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.01095481890496786</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4197,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4582,7 +4121,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4592,7 +4131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4603,68 +4142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.001802582320870938</v>
+        <v>-0.004825376533324266</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0211130349041182</v>
+        <v>-0.02758938328059446</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1989196555792887</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04690988384817812</v>
+        <v>0.0814304948965289</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.153917301860116</v>
+        <v>0.2145551922699243</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0.9862068965517241</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1972404039901224</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07379760643682176</v>
+        <v>-0.002241632203719979</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.696194308369228</v>
+        <v>1.009228221007628</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1989196555792887</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1595769883716971</v>
+        <v>0.2396919680726315</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08838783097671599</v>
+        <v>-0.02540469906843212</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.586665176447165</v>
+        <v>0.8811980485228851</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.03283823425413634</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.006660096326719822</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.07621007359576204</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0646249082548227</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4680,7 +4223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4711,7 +4254,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -4782,7 +4325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4800,89 +4343,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.004825376533324266</v>
+        <v>0.01474787186929194</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02758938328059446</v>
+        <v>-0.008463860883240582</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0814304948965289</v>
+        <v>0.04928522689999885</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2145551922699243</v>
+        <v>0.1178067050319378</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.05431928130163777</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.002241632203719979</v>
+        <v>0.1753965384342548</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.009228221007628</v>
+        <v>0.2779377375297312</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2396919680726315</v>
+        <v>0.07303432522764552</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02540469906843212</v>
+        <v>-0.1564241456440016</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8811980485228851</v>
+        <v>0.2685017165292968</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.03283823425413634</v>
+        <v>-0.01786396839384785</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.01966815465454008</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.1780372647039976</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.006616032910236935</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.07081338064522469</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.06908983233052379</v>
-      </c>
+        <v>-0.1344347201862501</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -4894,7 +4427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4925,62 +4458,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01474787186929194</v>
+        <v>0.002752546809440926</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.008463860883240582</v>
+        <v>-0.02018480026829717</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04928522689999885</v>
+        <v>0.07085501760958975</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1178067050319378</v>
+        <v>0.17619836208959</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9793103448275862</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.05431928130163777</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1753965384342548</v>
+        <v>0.03250488837758225</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2779377375297312</v>
+        <v>0.8661857671036176</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07303432522764552</v>
+        <v>0.207095220083988</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1564241456440016</v>
+        <v>-0.05103093383768187</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2685017165292968</v>
+        <v>0.7613601125805303</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.01786396839384785</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.01966815465454008</v>
+        <v>0.007614666978110529</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1780372647039976</v>
+        <v>0.03482458449137926</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1344347201862501</v>
+        <v>-0.02629423181576485</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4996,7 +4529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5014,89 +4547,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.002752546809440926</v>
+        <v>0.03273219043330289</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02018480026829717</v>
+        <v>0.009109077467205351</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07085501760958975</v>
+        <v>0.04678841119006954</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.17619836208959</v>
+        <v>0.1230466328024938</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9172413793103448</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.05431928130163777</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.03250488837758225</v>
+        <v>0.1753965384342548</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8661857671036176</v>
+        <v>0.2779377375297312</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.207095220083988</v>
+        <v>0.09205165127481774</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05103093383768187</v>
+        <v>-0.141473498967898</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7613601125805303</v>
+        <v>0.3384165774052922</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.01797016691891817</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.007614666978110529</v>
+        <v>0.03773967510927467</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03482458449137926</v>
+        <v>0.1780372647039976</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02629423181576485</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.000948255180545754</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.03845484271124511</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.04097893644734785</v>
-      </c>
+        <v>-0.1190943561789405</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5108,7 +4631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5139,180 +4662,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03273219043330289</v>
+        <v>0.008861833800013263</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.009109077467205351</v>
+        <v>-0.01421525945592816</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04678841119006954</v>
+        <v>0.06971703140278233</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1230466328024938</v>
+        <v>0.177351839171709</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9172413793103448</v>
+        <v>0.9724137931034482</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.05431928130163777</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1753965384342548</v>
+        <v>0.03250488837758225</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2779377375297312</v>
+        <v>0.8661857671036176</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09205165127481774</v>
+        <v>0.2144494682959772</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.141473498967898</v>
+        <v>-0.04524932362007883</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3384165774052922</v>
+        <v>0.7883971018666882</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01797016691891817</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.03773967510927467</v>
+        <v>0.01375357651872022</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1780372647039976</v>
+        <v>0.03482458449137926</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1190943561789405</v>
+        <v>-0.02036191281927813</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.008861833800013263</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.01421525945592816</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1710223654406263</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.06971703140278233</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.177351839171709</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9724137931034482</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1692846346126109</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.03250488837758225</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.8661857671036176</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1710223654406263</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.2144494682959772</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.04524932362007883</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.7883971018666882</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.02128572850164578</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.01375357651872022</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.03482458449137926</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.02036191281927813</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.007046549493602061</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.03845484271124511</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.04732111836863306</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5325,7 +4736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5710,7 +5121,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5720,7 +5131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5731,68 +5142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0001327025339010746</v>
+        <v>-0.2448392622096195</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08898835292102503</v>
+        <v>-0.3121310544082834</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.2314753634808069</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4109397789559724</v>
+        <v>0.4126693467586269</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.315814243187495</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>-0.03605992585647466</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>1.088190551974653</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4073175209111213</v>
+        <v>0.1037364199286095</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09012362424657316</v>
+        <v>-0.2863986423607316</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7450300267984358</v>
+        <v>0.1897456989979326</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.06365726930468618</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03513404329670899</v>
+        <v>-0.2714677903373722</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03870328381218169</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07108606303611287</v>
+        <v>-0.271467790337372</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5808,7 +5223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5839,23 +5254,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2448392622096195</v>
+        <v>-0.03609438697209466</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3121310544082834</v>
+        <v>-0.1219872743602687</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>-0.3158142431874948</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2314753634808069</v>
+        <v>0.1452308105053118</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4126693467586269</v>
+        <v>0.4573179251517301</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -5876,25 +5291,25 @@
         <v>-0.3158142431874948</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1037364199286095</v>
+        <v>0.4088361288293452</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2863986423607316</v>
+        <v>-0.08914179502303765</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1897456989979326</v>
+        <v>0.7478077332311958</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06365726930468618</v>
+        <v>-0.07905225979655861</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2714677903373722</v>
+        <v>-0.07008369076470933</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.271467790337372</v>
+        <v>-0.07008369076470922</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5910,7 +5325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5928,91 +5343,85 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03609438697209466</v>
+        <v>0.0559351665859209</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1219872743602687</v>
+        <v>-0.03815840349701582</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1452308105053118</v>
+        <v>0.01074210777091695</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4573179251517301</v>
+        <v>0.1173189306920863</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>0.3688524590163935</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.315814243187495</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.03605992585647466</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.088190551974653</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4088361288293452</v>
+        <v>0.05517726065668538</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08914179502303765</v>
+        <v>-0.3177937121949841</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7478077332311958</v>
+        <v>0.1009254792029551</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07905225979655861</v>
+        <v>-0.04992556603898313</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.07008369076470933</v>
+        <v>0.01870071055899558</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.462641195899576</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07008369076470922</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.03622228271729544</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.03726115476417413</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.001079079806553418</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>-0.3035197467329239</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.03723595092910825</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.03530206183892504</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6022,7 +5431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6053,62 +5462,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0559351665859209</v>
+        <v>0.01669705347853823</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.03815840349701582</v>
+        <v>-0.07390003854170746</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.01074210777091695</v>
+        <v>0.1169348467690823</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1173189306920863</v>
+        <v>0.4128996071628967</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.3688524590163935</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.00124772041103749</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.9969484920130616</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.05517726065668538</v>
+        <v>0.4306257291597344</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.3177937121949841</v>
+        <v>-0.07505411240476501</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.1009254792029551</v>
+        <v>0.7876633880573466</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04992556603898313</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.01870071055899558</v>
+        <v>-0.01915378559603187</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.462641195899576</v>
+        <v>0.03870328381218169</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3035197467329239</v>
+        <v>-0.05570124819079214</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6117,7 +5526,7 @@
         <v>0.03723595092910825</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.03530206183892504</v>
+        <v>-0.02072738717352474</v>
       </c>
     </row>
     <row r="8">
@@ -6128,7 +5537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6146,95 +5555,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01669705347853823</v>
+        <v>-0.0586052265845145</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.07390003854170746</v>
+        <v>-0.1424921903783969</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1169348467690823</v>
+        <v>0.08593293335824043</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4128996071628967</v>
+        <v>0.1318348326886688</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9672131147540983</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.08742035038740836</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>0.2857211456836861</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>0.3012213710874782</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4306257291597344</v>
+        <v>0.03157546173106818</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07505411240476501</v>
+        <v>-0.3330530399221047</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7876633880573466</v>
+        <v>0.05775510723685248</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.009244063411533276</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01915378559603187</v>
+        <v>-0.09180075165453216</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03870328381218169</v>
+        <v>0.333818543467101</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05570124819079214</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.01656215310495335</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01656215310495313</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.02072738717352474</v>
-      </c>
+        <v>-0.3190983490267625</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6244,7 +5639,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6275,23 +5670,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0586052265845145</v>
+        <v>-0.02956520551904285</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1424921903783969</v>
+        <v>-0.116039903241864</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08593293335824043</v>
+        <v>0.1331205105803096</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1318348326886688</v>
+        <v>0.414844741196839</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -6300,155 +5695,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.08742035038740836</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2857211456836861</v>
+        <v>-0.0164327516352607</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3012213710874782</v>
+        <v>1.040189029865013</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.03157546173106818</v>
+        <v>0.3900752392253577</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3330530399221047</v>
+        <v>-0.1012713180234582</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.05775510723685248</v>
+        <v>0.713491934457906</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.009244063411533276</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.09180075165453216</v>
+        <v>-0.06378474174201731</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.333818543467101</v>
+        <v>0.0203614049749441</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3190983490267625</v>
+        <v>-0.0824670026783576</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.02956520551904285</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.116039903241864</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1331205105803096</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.414844741196839</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-0.0164327516352607</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.040189029865013</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3900752392253577</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1012713180234582</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.713491934457906</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.0790522597965585</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.06378474174201731</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.0203614049749441</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.0824670026783576</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.02969396758820342</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.01765843925121746</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.01225187736922417</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6461,7 +5744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6846,7 +6129,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6856,7 +6139,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6867,74 +6150,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.01525424958956756</v>
+        <v>0.07378636095717539</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.07188507109342634</v>
+        <v>0.01203498633555444</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2622253758368088</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.121880142964137</v>
+        <v>0.1497348611482323</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1646297036067336</v>
+        <v>0.1797026712816814</v>
       </c>
       <c r="O4" s="2" t="n">
+        <v>0.9454191033138402</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2202351424839316</v>
+        <v>-0.2207723013756367</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1298177948297481</v>
+        <v>0.1290394939501307</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7108227256560352</v>
+        <v>0.7125564396455729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2595355160283203</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2628752641499237</v>
+        <v>0.3780135932703899</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1785268977406829</v>
+        <v>-0.1036318997178892</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.489224968503877</v>
+        <v>0.7035035755827982</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.09340275911067697</v>
+        <v>-0.07471818073633707</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.09658828590192492</v>
+        <v>-0.01490189064218872</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.08751745111813558</v>
+        <v>0.08676828979966644</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1692899151464387</v>
+        <v>-0.09355276685575453</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.9069015013894919</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.4748825853361665</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6944,7 +6235,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6975,62 +6266,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.07378636095717539</v>
+        <v>0.05464882401835514</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01203498633555444</v>
+        <v>-0.006001987906799067</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2622253758368088</v>
+        <v>-0.2622253758368087</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1497348611482323</v>
+        <v>0.1483624000303649</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1797026712816814</v>
+        <v>0.1979857514979584</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2207723013756367</v>
+        <v>-0.2570551024208101</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1290394939501307</v>
+        <v>0.07646857609973301</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7125564396455729</v>
+        <v>0.8296614540519247</v>
       </c>
       <c r="T5" s="2" t="n">
         <v>-0.2595355160283203</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3780135932703899</v>
+        <v>0.4195518772049187</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1036318997178892</v>
+        <v>-0.07661214255351512</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7035035755827982</v>
+        <v>0.7808085503026149</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07471818073633707</v>
+        <v>-0.09340275911067686</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01490189064218872</v>
+        <v>-0.03245878290834869</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.08676828979966644</v>
+        <v>0.03616562550703994</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.09355276685575453</v>
+        <v>-0.06622918839042524</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7039,7 +6330,7 @@
         <v>0.9069015013894919</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.4748825853361665</v>
+        <v>-0.1655269949776802</v>
       </c>
     </row>
     <row r="6">
@@ -7050,7 +6341,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7068,94 +6359,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05464882401835514</v>
+        <v>0.3088639259249495</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.006001987906799067</v>
+        <v>0.2335936956842988</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2622253758368087</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1483624000303649</v>
+        <v>0.05838140064822201</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1979857514979584</v>
+        <v>0.1033489193909851</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.9064327485380117</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2570551024208101</v>
+        <v>-0.07121848839623379</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.07646857609973301</v>
+        <v>0.3457311767825897</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8296614540519247</v>
+        <v>0.2298621349342879</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2595355160283203</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4195518772049187</v>
+        <v>0.4092269382762355</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.07661214255351512</v>
+        <v>-0.08332829247992346</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7808085503026149</v>
+        <v>0.7615932850758771</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.09340275911067686</v>
+        <v>-0.07471818073633718</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03245878290834869</v>
+        <v>0.2007596908625031</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03616562550703994</v>
+        <v>0.2953470426488958</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.06622918839042524</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.07098591040254587</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.04721931179890304</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.1240634110926691</v>
-      </c>
+        <v>-0.073020857478447</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.9069015013894919</v>
+        <v>0.05128529554140782</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.1655269949776802</v>
+        <v>-0.04968647066593979</v>
       </c>
     </row>
     <row r="7">
@@ -7166,7 +6447,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7197,62 +6478,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3088639259249495</v>
+        <v>0.1448569321946125</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2335936956842988</v>
+        <v>0.07901842662345748</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.05838140064822201</v>
+        <v>0.134682406219364</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1033489193909851</v>
+        <v>0.1793149283746856</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9064327485380117</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.07121848839623379</v>
+        <v>-0.2484463964898045</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3457311767825897</v>
+        <v>0.08894191220555525</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2298621349342879</v>
+        <v>0.8018763161069433</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4092269382762355</v>
+        <v>0.5233203950422964</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08332829247992346</v>
+        <v>-0.009112961371831707</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7615932850758771</v>
+        <v>0.9739273286511628</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07471818073633718</v>
+        <v>-0.07471818073633707</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2007596908625031</v>
+        <v>0.05029868174594498</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2953470426488958</v>
+        <v>0.04817196029024085</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.073020857478447</v>
+        <v>0.002028981442239175</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7261,7 +6542,7 @@
         <v>0.05128529554140782</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.04968647066593979</v>
+        <v>0.006526314267764954</v>
       </c>
     </row>
     <row r="8">
@@ -7272,7 +6553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7290,94 +6571,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1448569321946125</v>
+        <v>0.3367420067828579</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.07901842662345748</v>
+        <v>0.2598685620878403</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.1037854592728726</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.134682406219364</v>
+        <v>0.04136027603732909</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1793149283746856</v>
+        <v>0.09993932957921133</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2484463964898045</v>
+        <v>-0.03397181375486624</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08894191220555525</v>
+        <v>0.3996986714733644</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8018763161069433</v>
+        <v>0.1096461580852159</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.08900501376493108</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5233203950422964</v>
+        <v>0.383750521792388</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.009112961371831707</v>
+        <v>-0.0999001515364264</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9739273286511628</v>
+        <v>0.7141803073192724</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07471818073633707</v>
+        <v>-0.07471818073633718</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05029868174594498</v>
+        <v>0.2263352110443477</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.04817196029024085</v>
+        <v>0.3472939959876744</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.002028981442239175</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.1625913914504808</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.03617918111331597</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.2062318728427115</v>
-      </c>
+        <v>-0.08977905735759928</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
         <v>0.05128529554140782</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.006526314267764954</v>
+        <v>-0.04873520817013055</v>
       </c>
     </row>
     <row r="9">
@@ -7388,7 +6659,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7419,62 +6690,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3367420067828579</v>
+        <v>0.1800763928270799</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2598685620878403</v>
+        <v>0.112212484264637</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1037854592728726</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04136027603732909</v>
+        <v>0.115776016655172</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.09993932957921133</v>
+        <v>0.1763606768759317</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.935672514619883</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03397181375486624</v>
+        <v>-0.2312883050997221</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.3996986714733644</v>
+        <v>0.1138026337307372</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1096461580852159</v>
+        <v>0.7464975007580551</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08900501376493108</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.383750521792388</v>
+        <v>0.5351352147441528</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.0999001515364264</v>
+        <v>-0.001427676159082236</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7141803073192724</v>
+        <v>0.9959153419213013</v>
       </c>
       <c r="X9" s="2" t="n">
         <v>-0.07471818073633718</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.2263352110443477</v>
+        <v>0.08260922818529304</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3472939959876744</v>
+        <v>0.07210189716125437</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.08977905735759928</v>
+        <v>0.009800683173736058</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7483,122 +6754,6 @@
         <v>0.05128529554140782</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.04873520817013055</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.1800763928270799</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.112212484264637</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.115776016655172</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1763606768759317</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.935672514619883</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2312883050997221</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1138026337307372</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7464975007580551</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.5351352147441528</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.001427676159082236</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.9959153419213013</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.07471818073633718</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.08260922818529304</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.07210189716125437</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0.009800683173736058</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.1983564207667161</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.01417499456310478</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.2155873650573834</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>0.007178166975881028</v>
       </c>
     </row>
@@ -7613,7 +6768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7998,7 +7153,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8008,7 +7163,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8019,74 +7174,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>0.01733422320252243</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.2963414873615395</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>-0.02542419299884719</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.2152266720452529</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.03198399714010954</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.04447864517159239</v>
+        <v>0.03913486734061711</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0878684466295574</v>
+        <v>0.2445033638472462</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1216572575582907</v>
+        <v>-0.1650204430719699</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.2134223460531468</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1592570553973541</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8096,7 +7259,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8127,62 +7290,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.06676653353273054</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.06452511043579368</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.06599576241334662</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2156952619322512</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.13318215211393</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.5391526104926985</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.06155253189821752</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.1744708581765999</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.2152897169169782</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03913486734061711</v>
+        <v>-0.04447864517159239</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2445033638472462</v>
+        <v>0.0878684466295574</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1650204430719699</v>
+        <v>-0.1216572575582907</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8191,7 +7354,7 @@
         <v>0.2134223460531468</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1592570553973541</v>
+        <v>-0.1114588698733576</v>
       </c>
     </row>
     <row r="6">
@@ -8202,7 +7365,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8220,95 +7383,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>0.02787440931566798</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>0.03034313930079358</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0.04971417837815464</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>0.1212599950451121</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>0.9204545454545454</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06387704928419313</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.2066569106734957</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>0.2849094544886638</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.09801218796067679</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.1461175664873063</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.3428131313161925</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.02289602556240811</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.04447864517159239</v>
+        <v>0.05242255391963346</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0878684466295574</v>
+        <v>0.158405095403602</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1216572575582907</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.2134223460531468</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.1114588698733576</v>
-      </c>
+        <v>-0.0914900511958151</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8318,7 +7467,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8349,62 +7498,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02787440931566798</v>
+        <v>-0.02989700063240341</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.03034313930079358</v>
+        <v>-0.02756702496466246</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04971417837815464</v>
+        <v>0.09099260937618169</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1212599950451121</v>
+        <v>0.2258051820804493</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9204545454545454</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.06387704928419313</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2066569106734957</v>
+        <v>0.07720953785198659</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2849094544886638</v>
+        <v>0.7328334660509549</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09801218796067679</v>
+        <v>0.1608298545088545</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1461175664873063</v>
+        <v>-0.09726664974168286</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3428131313161925</v>
+        <v>0.5625278567949983</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02289602556240811</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05242255391963346</v>
+        <v>-0.006728578018330045</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.158405095403602</v>
+        <v>0.03413406613534886</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.0914900511958151</v>
+        <v>-0.03951387493343739</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8420,7 +7569,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8438,40 +7587,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.02989700063240341</v>
+        <v>-0.08141038848245086</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02756702496466246</v>
+        <v>-0.07920413672890436</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09099260937618169</v>
+        <v>0.1031106325266614</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2258051820804493</v>
+        <v>0.1421782585002016</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -8480,47 +7625,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1139317855593476</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.07720953785198659</v>
+        <v>0.1421366535938349</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7328334660509549</v>
+        <v>0.508167538049784</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1608298545088545</v>
+        <v>0.0367030399543522</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.09726664974168286</v>
+        <v>-0.1937953655775521</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.5625278567949983</v>
+        <v>0.1283746880604574</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.01232164979750494</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.006728578018330045</v>
+        <v>-0.05947223104719934</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03413406613534886</v>
+        <v>0.09646487536532056</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03951387493343739</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.03950729825398969</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.04939418976686816</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.0935208759128614</v>
-      </c>
+        <v>-0.1422180590696667</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -8532,7 +7671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8563,23 +7702,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.08141038848245086</v>
+        <v>-0.1091436876433024</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.07920413672890436</v>
+        <v>-0.1070040452212114</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1031106325266614</v>
+        <v>0.1241198546184887</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1421782585002016</v>
+        <v>0.2362392793851624</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -8588,155 +7727,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1139317855593476</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1421366535938349</v>
+        <v>0.05090485257089106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.508167538049784</v>
+        <v>0.8238550132417071</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.0367030399543522</v>
+        <v>0.09268548955178169</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1937953655775521</v>
+        <v>-0.1502599378105456</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1283746880604574</v>
+        <v>0.3241821610345889</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01232164979750494</v>
+        <v>-0.04770980148098947</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.05947223104719934</v>
+        <v>-0.08786786894513343</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09646487536532056</v>
+        <v>0.00888125301749132</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1422180590696667</v>
+        <v>-0.09589743259997674</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.1091436876433024</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.1070040452212114</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1241198546184887</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2362392793851624</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.05090485257089106</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.8238550132417071</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.09268548955178169</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1502599378105456</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.3241821610345889</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04770980148098947</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.08786786894513343</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.00888125301749132</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.09589743259997674</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04540895245751253</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.07260730270905902</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.02932775978395874</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>2.089923077804836</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,19 +967,19 @@
         <v>1.610428448490837</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
@@ -986,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,19 +995,19 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1014,7 +1015,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>1.924141575557356</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,27 +1132,27 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,19 +1241,19 @@
         <v>3.682584690591698</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,19 +1269,19 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,27 +1378,27 @@
         <v>3.449946282588622</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,27 +1406,27 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,11 +1515,11 @@
         <v>3.847068823288041</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
@@ -1526,7 +1527,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,11 +1543,11 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
@@ -1554,7 +1555,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>3.486808642003445</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,11 +1680,11 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1691,15 +1692,15 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.1450386949103385</v>
+        <v>0.0446584681315485</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05692592411839026</v>
+        <v>-0.01115218753601177</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.3385720911587933</v>
+        <v>0.0887235763107324</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1772354841845319</v>
+        <v>0.3128011051560898</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5206292358486946</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.0947431452773746</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.106641411765261</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7835073997541646</v>
+        <v>0.2596730744822084</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.04177512819891538</v>
+        <v>-0.01000494626196236</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.100448980212525</v>
+        <v>0.9532666348445535</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1420856921406376</v>
+        <v>-0.1039903280688754</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1456635683267122</v>
+        <v>-0.118791889136512</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.2637362703305421</v>
+        <v>-0.1658702443570722</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1180176287204635</v>
+        <v>0.1092255124148501</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.09464838563953046</v>
+        <v>0.2302799634593125</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.135721852795745</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.6321264784029936</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.2884882608262321</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3255727592241868</v>
+        <v>0.06258089522353627</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2257118017182801</v>
+        <v>-0.1649025038498633</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4572722746277164</v>
+        <v>0.2297360999566683</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.06754810166434866</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.3400180353268318</v>
+        <v>-0.1564629611057515</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.802942965732178</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2567607180060474</v>
+        <v>-0.1564629611057515</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1019117619885797</v>
+        <v>0.05887936950553474</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2154753793582211</v>
+        <v>0.002308965217657111</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.209955706117895</v>
+        <v>0.0861551473530274</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1577159972003161</v>
+        <v>0.2957227627382383</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9811634349030471</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3910419629857261</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1499730030920461</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.831192718696548</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.8095036028939888</v>
+        <v>0.2768209626218772</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.05695992522437687</v>
+        <v>0.003471823849444</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.136961073453244</v>
+        <v>1.016216979828099</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.04325670276229032</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.288844016014292</v>
+        <v>0.01361296711586646</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2703278600904964</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.01457588745827887</v>
+        <v>0.01361296711586646</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,58 +2345,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.3197093201867722</v>
+        <v>-0.0389859986746377</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2495981977471486</v>
+        <v>-0.09032796655779096</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.4349106047534014</v>
+        <v>0.105146290017862</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.161933865159753</v>
+        <v>0.2410269901264382</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.5564315251194953</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1623531669993604</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.182742201377048</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.595666574932973</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5336768015276447</v>
+        <v>0.1588126632765954</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.104154910292273</v>
+        <v>-0.08927258342455358</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7495578116919465</v>
+        <v>0.5830054324818104</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1420856921406376</v>
+        <v>-0.008645597557340956</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.2043023751327736</v>
+        <v>-0.08006872040753255</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.07468600913571855</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1400782515738124</v>
+        <v>-0.08006872040753266</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -2446,58 +2447,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1719997770634127</v>
+        <v>0.07519308291442628</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.08666562986286497</v>
+        <v>0.01775112196999706</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3526760396798082</v>
+        <v>0.08617808970119449</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1723863215905274</v>
+        <v>0.2971337096776321</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5277315235233264</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1081552994646565</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.121737924058131</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7532405065733498</v>
+        <v>0.2964924113803935</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.02409575298131195</v>
+        <v>0.01893189628037817</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.057938632836764</v>
+        <v>1.088431381717628</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1420856921406376</v>
+        <v>-0.04325670276229032</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.03153485659827238</v>
+        <v>0.02922927991718782</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.01481585487843839</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.01697043319527958</v>
+        <v>0.02922927991718782</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2548,67 +2549,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2925695514340041</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.4257824628723899</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1911504799548355</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09955264025319233</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.09507811762339856</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9224376731301939</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1379451935448507</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.6279278609569019</v>
+        <v>0.2117597153840092</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.293214159365938</v>
+        <v>-0.03587709265072067</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1911504799548355</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4994053066639372</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1241734372465926</v>
+        <v>-0.2060850325577077</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7014229356397752</v>
+        <v>0.03737143334716839</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08307751008271946</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.5118456750489424</v>
+        <v>-0.02711604064754702</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.798304925794465</v>
+        <v>0.2131655745487826</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.159294036643407</v>
+        <v>-0.1980616827885991</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>0.08270819824638442</v>
+        <v>0.1034278830282558</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>-0.06916594252835273</v>
+        <v>-0.08435133805704931</v>
       </c>
     </row>
     <row r="9">
@@ -2654,67 +2655,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.155136892308279</v>
+        <v>0.06949778383754923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.274185920164117</v>
+        <v>0.01236009303058605</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4341707534324699</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2020371883620518</v>
+        <v>0.07842385788493024</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.154911528137777</v>
+        <v>0.2702499091159425</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9822714681440443</v>
+        <v>0.9</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3466732867683084</v>
+        <v>-0.1581346033647495</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.233760024087988</v>
+        <v>0.01396416978886927</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7368833501353319</v>
+        <v>0.9316906731955904</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4341707534324699</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.7680845875632039</v>
+        <v>0.2703904782309559</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.0327664175259792</v>
+        <v>-0.001581985642172379</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.0787873877976</v>
+        <v>0.9926105037697811</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.04325670276229021</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.3510984478848871</v>
+        <v>0.02377745116107444</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3628839347104611</v>
+        <v>0.01514055055376207</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.008647461845735283</v>
+        <v>0.008508083538383726</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.08270819824638442</v>
+        <v>0.1034278830282558</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.1361240023967677</v>
+        <v>-0.03985989506857002</v>
       </c>
     </row>
   </sheetData>
@@ -2958,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2988,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3000,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3046,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2562066685833588</v>
+        <v>-0.1452922176580209</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1919533832463862</v>
+        <v>-0.05948570666158792</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1643751024664248</v>
+        <v>0.3387400714875508</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2154447623434743</v>
+        <v>0.1773285455590618</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4375057689528338</v>
+        <v>-0.5219321743416376</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1329400080149157</v>
+        <v>-0.0966927494825881</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8689130665823445</v>
+        <v>1.108705095999487</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.233279204028003</v>
+        <v>0.7878379101645963</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.05208870267973964</v>
+        <v>0.04118979760174413</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.098484212603029</v>
+        <v>1.098628363783892</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.1420856921406376</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3148,68 +3149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1456481924702164</v>
+        <v>0.142335661513231</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.08704982482296564</v>
+        <v>0.2570179418508092</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.02913535421699465</v>
+        <v>0.1180821853088314</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07336880208048525</v>
+        <v>0.09469571173316994</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.3379360465116279</v>
+        <v>0.9728230726566833</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.138070976586378</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>0.6286114532152427</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>0.2932948051038192</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1207562771902446</v>
+        <v>0.325324511047411</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.4720162998148467</v>
+        <v>-0.2281658468205077</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.1075578535930514</v>
+        <v>0.4536602398279374</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.06754810166434866</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.08800978284713346</v>
+        <v>0.3365218910059817</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.8172807306068304</v>
+        <v>0.8029429657321787</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.4981566679308087</v>
+        <v>-0.2586998499626871</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.1068371958786292</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3254,68 +3251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.309825691595069</v>
+        <v>0.1003096102673791</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2428298651848617</v>
+        <v>0.2107727774731185</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4380050570761584</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1208509365587099</v>
+        <v>0.2100720551935929</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2020934073527834</v>
+        <v>0.1577995686478441</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9382267441860465</v>
+        <v>0.9816971713810316</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.3926971220532957</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>0.1474963665540145</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>0.8341798452145895</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4380050570761584</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.093541190435257</v>
+        <v>0.8117971282921208</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01374130423147568</v>
+        <v>0.05514301636451036</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9740192890635779</v>
+        <v>1.132039140631993</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.04268328162290125</v>
+        <v>0.2873518095885685</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.112279471679261</v>
+        <v>0.2703278600904973</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.0625707763457034</v>
+        <v>0.01340122501671237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.007149815379016156</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3360,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4050864704605563</v>
+        <v>-0.3199110476349527</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.3332181830461667</v>
+        <v>-0.2516350106369474</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2161164061045036</v>
+        <v>-0.6098774505571758</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.08273142359005452</v>
+        <v>0.4350832565542558</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1180962070563869</v>
+        <v>0.1620178744908965</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9345930232558139</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1729422453751833</v>
+        <v>-0.5576371523362509</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.6658069850939825</v>
+        <v>-0.1641571630470918</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.343473817797331</v>
+        <v>1.184550757564826</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2019757611901184</v>
+        <v>-0.595666574932973</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6988976436088852</v>
+        <v>0.5374007016113604</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1996562657161938</v>
+        <v>-0.1046582488027999</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6225095057326417</v>
+        <v>0.7493973644708927</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.122741906631302</v>
+        <v>-0.1420856921406376</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1185153729880222</v>
+        <v>-0.2043023751327734</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.4703399767942977</v>
+        <v>-0.07468600913571788</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2392811250179974</v>
+        <v>-0.1400782515738127</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3462,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4342011775436574</v>
+        <v>-0.1722453050076025</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3608437119323213</v>
+        <v>-0.08914469003064007</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1197392093328651</v>
+        <v>0.3528455767240981</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2064344599986419</v>
+        <v>0.1724765375493502</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3609757233342479</v>
+        <v>-0.5290151578686424</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2870819453199265</v>
+        <v>-0.1100760186168951</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7169197413667834</v>
+        <v>1.123750997205283</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.244361020252491</v>
+        <v>0.7574975263461594</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.05730930099719478</v>
+        <v>0.02352035569793709</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.108354808109552</v>
+        <v>1.0563191453508</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.1420856921406376</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1416920586490957</v>
+        <v>-0.03153485659827227</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1360548097997625</v>
+        <v>-0.01481585487843817</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.004962127531792815</v>
+        <v>-0.0169704331952798</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3564,64 +3557,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2182581518238311</v>
+        <v>0.2954135518623191</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1559458821942616</v>
+        <v>0.4254637508651029</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1616586033180829</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07146802938810665</v>
+        <v>0.09960779303170926</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1071587332980531</v>
+        <v>0.09512601301536631</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.922906267332224</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.09542945485596188</v>
+        <v>-0.1381411092884852</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.8219283045048862</v>
+        <v>0.6284789377542312</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.1895287014377966</v>
+        <v>0.2934437832432116</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1194163443509543</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3467806998179932</v>
+        <v>0.5030459925903645</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.3655371183728369</v>
+        <v>-0.1246655281701697</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3088782513654108</v>
+        <v>0.7014902286590058</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1366025849960363</v>
+        <v>-0.08307751008271946</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03020881651768559</v>
+        <v>0.5156215710505936</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.6081419065579503</v>
+        <v>0.8027962654140584</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.396949249610661</v>
+        <v>-0.1592940366434071</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.08565903934550501</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.07148494660096649</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3666,64 +3663,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4103901676897292</v>
+        <v>0.1605366293762784</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3382506032793406</v>
+        <v>0.2770461559158357</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3799797244656153</v>
+        <v>-0.4341707534324698</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.124023134579484</v>
+        <v>0.2021490720431115</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2048556913882314</v>
+        <v>0.1549922091779806</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9273255813953488</v>
+        <v>0.9822518025513034</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3723569839339401</v>
+        <v>-0.3452091717905148</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2641585360415228</v>
+        <v>0.237224659240322</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7395236171349165</v>
+        <v>0.7333044153345905</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3799797244656153</v>
+        <v>-0.4341707534324698</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.247121582790439</v>
+        <v>0.7723776500500885</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.05860979072278649</v>
+        <v>0.0321861485528141</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.110813646591491</v>
+        <v>1.077069258726702</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.122741906631302</v>
+        <v>-0.1144491365988818</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1227373671565088</v>
+        <v>0.3578168508028554</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1158212501088403</v>
+        <v>0.3696609415363854</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.006198230269403471</v>
+        <v>-0.008647461845735394</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.08565903934550501</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.1403984132052861</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3966,28 +3967,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3996,10 +3997,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4008,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4054,49 +4055,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.004825376533324266</v>
+        <v>0.2562066685833588</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02758938328059446</v>
+        <v>0.1919533832463862</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.0814304948965289</v>
+        <v>0.1643751024664248</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2145551922699243</v>
+        <v>0.2154447623434743</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528338</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.002241632203719979</v>
+        <v>0.1329400080149157</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.009228221007628</v>
+        <v>0.8689130665823445</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2396919680726315</v>
+        <v>1.233279204028003</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02540469906843212</v>
+        <v>0.05208870267973964</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8811980485228851</v>
+        <v>1.098484212603029</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.03283823425413634</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4156,64 +4157,68 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.004825376533324266</v>
+        <v>0.1456481924702164</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.02758938328059446</v>
+        <v>0.08704982482296564</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0814304948965289</v>
+        <v>0.02913535421699465</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2145551922699243</v>
+        <v>0.07336880208048525</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.3379360465116279</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1972404039901224</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.002241632203719979</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.009228221007628</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2396919680726315</v>
+        <v>0.1207562771902446</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.02540469906843212</v>
+        <v>-0.4720162998148467</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.8811980485228851</v>
+        <v>0.1075578535930514</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.03283823425413634</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0</v>
+        <v>-0.08800978284713346</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0</v>
+        <v>0.8172807306068304</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0</v>
+        <v>-0.4981566679308087</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1068371958786292</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4258,64 +4263,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.004825376533324266</v>
+        <v>0.309825691595069</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.02758938328059446</v>
+        <v>0.2428298651848617</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0814304948965289</v>
+        <v>0.1208509365587099</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2145551922699243</v>
+        <v>0.2020934073527834</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9382267441860465</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.002241632203719979</v>
+        <v>0.2601459135591284</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.009228221007628</v>
+        <v>0.7434803069533858</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2396919680726315</v>
+        <v>1.093541190435257</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02540469906843212</v>
+        <v>-0.01374130423147568</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.8811980485228851</v>
+        <v>0.9740192890635779</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.03283823425413634</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.04268328162290125</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.112279471679261</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.0625707763457034</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.007149815379016156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4360,58 +4369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.01474787186929194</v>
+        <v>0.4050864704605563</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.008463860883240582</v>
+        <v>0.3332181830461667</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04928522689999885</v>
+        <v>0.08273142359005452</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1178067050319378</v>
+        <v>0.1180962070563869</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9345930232558139</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.05431928130163777</v>
+        <v>-0.1729422453751833</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1753965384342548</v>
+        <v>0.6658069850939825</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.2779377375297312</v>
+        <v>0.343473817797331</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.2019757611901184</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.07303432522764552</v>
+        <v>0.6988976436088852</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1564241456440016</v>
+        <v>-0.1996562657161938</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2685017165292968</v>
+        <v>0.6225095057326417</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.01786396839384785</v>
+        <v>-0.122741906631302</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.01966815465454008</v>
+        <v>0.1185153729880222</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1780372647039976</v>
+        <v>0.4703399767942977</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1344347201862501</v>
+        <v>-0.2392811250179974</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4462,58 +4471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.002752546809440926</v>
+        <v>0.4342011775436574</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.02018480026829717</v>
+        <v>0.3608437119323213</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07085501760958975</v>
+        <v>0.1197392093328651</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.17619836208959</v>
+        <v>0.2064344599986419</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9244186046511628</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.03250488837758225</v>
+        <v>0.2870819453199265</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8661857671036176</v>
+        <v>0.7169197413667834</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.207095220083988</v>
+        <v>1.244361020252491</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.05103093383768187</v>
+        <v>0.05730930099719478</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7613601125805303</v>
+        <v>1.108354808109552</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.007614666978110529</v>
+        <v>0.1416920586490957</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.03482458449137926</v>
+        <v>0.1360548097997625</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.02629423181576485</v>
+        <v>0.004962127531792815</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4564,58 +4573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03273219043330289</v>
+        <v>0.2182581518238311</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.009109077467205351</v>
+        <v>0.1559458821942616</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04678841119006954</v>
+        <v>0.07146802938810665</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1230466328024938</v>
+        <v>0.1071587332980531</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9172413793103448</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.05431928130163777</v>
+        <v>-0.09542945485596188</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1753965384342548</v>
+        <v>0.8219283045048862</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.2779377375297312</v>
+        <v>0.1895287014377966</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1194163443509543</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.09205165127481774</v>
+        <v>0.3467806998179932</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.141473498967898</v>
+        <v>-0.3655371183728369</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3384165774052922</v>
+        <v>0.3088782513654108</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.01797016691891817</v>
+        <v>-0.1366025849960363</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.03773967510927467</v>
+        <v>-0.03020881651768559</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1780372647039976</v>
+        <v>0.6081419065579503</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1190943561789405</v>
+        <v>-0.396949249610661</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4666,58 +4675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.008861833800013263</v>
+        <v>0.4103901676897292</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.01421525945592816</v>
+        <v>0.3382506032793406</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06971703140278233</v>
+        <v>0.124023134579484</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.177351839171709</v>
+        <v>0.2048556913882314</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.9273255813953488</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3723569839339401</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.03250488837758225</v>
+        <v>0.2641585360415228</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8661857671036176</v>
+        <v>0.7395236171349165</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2144494682959772</v>
+        <v>1.247121582790439</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.04524932362007883</v>
+        <v>0.05860979072278649</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7883971018666882</v>
+        <v>1.110813646591491</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.122741906631302</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.01375357651872022</v>
+        <v>0.1227373671565088</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.03482458449137926</v>
+        <v>0.1158212501088403</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.02036191281927813</v>
+        <v>0.006198230269403471</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4966,28 +4975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4996,10 +5005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5008,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5054,49 +5063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03655092770721002</v>
+        <v>-0.00716512238730771</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05581532776669107</v>
+        <v>-0.0255932030004653</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1254404790617945</v>
+        <v>0.08136015489054858</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4644648305065673</v>
+        <v>0.2138357999046741</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.315814243187495</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.03605992585647466</v>
+        <v>-0.0001934176492057738</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.088190551974653</v>
+        <v>1.00077866304843</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.5150138940867595</v>
+        <v>0.2396919680726315</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02049442951914759</v>
+        <v>-0.02540469906843212</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9420189302309699</v>
+        <v>0.8811980485228851</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06320652629413515</v>
+        <v>-0.03283823425413634</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5156,19 +5165,19 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.2448392622096195</v>
+        <v>-0.00716512238730771</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3121310544082834</v>
+        <v>-0.0255932030004653</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2314753634808069</v>
+        <v>0.08136015489054858</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4126693467586269</v>
+        <v>0.2138357999046741</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>1</v>
@@ -5177,37 +5186,37 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.315814243187495</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.03605992585647466</v>
+        <v>-0.0001934176492057738</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.088190551974653</v>
+        <v>1.00077866304843</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1037364199286095</v>
+        <v>0.2396919680726315</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2863986423607316</v>
+        <v>-0.02540469906843212</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.1897456989979326</v>
+        <v>0.8811980485228851</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.06365726930468618</v>
+        <v>-0.03283823425413634</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.2714677903373722</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.271467790337372</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5258,19 +5267,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.03609438697209466</v>
+        <v>-0.00716512238730771</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1219872743602687</v>
+        <v>-0.0255932030004653</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1452308105053118</v>
+        <v>0.08136015489054858</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4573179251517301</v>
+        <v>0.2138357999046741</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -5279,37 +5288,37 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.315814243187495</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.03605992585647466</v>
+        <v>-0.0001934176492057738</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.088190551974653</v>
+        <v>1.00077866304843</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4088361288293452</v>
+        <v>0.2396919680726315</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.08914179502303765</v>
+        <v>-0.02540469906843212</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7478077332311958</v>
+        <v>0.8811980485228851</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07905225979655861</v>
+        <v>-0.03283823425413634</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.07008369076470933</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.07008369076470922</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5360,68 +5369,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0559351665859209</v>
+        <v>0.01236210753200018</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.03815840349701582</v>
+        <v>-0.006428419420643317</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.01074210777091695</v>
+        <v>0.04934189613782423</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1173189306920863</v>
+        <v>0.1174440626156266</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.3688524590163935</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.05654266249383377</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.1778094115055817</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.2841727785903324</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.05517726065668538</v>
+        <v>0.07303432522764552</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.3177937121949841</v>
+        <v>-0.1564241456440016</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.1009254792029551</v>
+        <v>0.2685017165292968</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04992556603898313</v>
+        <v>-0.01786396839384785</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.01870071055899558</v>
+        <v>0.01966815465454008</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.462641195899576</v>
+        <v>0.1780372647039976</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.3035197467329239</v>
+        <v>-0.1344347201862501</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.03530206183892504</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5466,68 +5471,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01669705347853823</v>
+        <v>0.0003949845699660059</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.07390003854170746</v>
+        <v>-0.01817341974010656</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1169348467690823</v>
+        <v>0.07082321100460236</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4128996071628967</v>
+        <v>0.1756174005597951</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>0.0346244311529067</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>0.8606085575830302</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4306257291597344</v>
+        <v>0.207095220083988</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07505411240476501</v>
+        <v>-0.05103093383768187</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7876633880573466</v>
+        <v>0.7613601125805303</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01915378559603187</v>
+        <v>0.007614666978110529</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.03870328381218169</v>
+        <v>0.03482458449137948</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.05570124819079214</v>
+        <v>-0.02629423181576485</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.02072738717352474</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5572,58 +5573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0586052265845145</v>
+        <v>0.03030414333095188</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1424921903783969</v>
+        <v>0.01118059294256613</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.08593293335824043</v>
+        <v>0.04684196621151677</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1318348326886688</v>
+        <v>0.1226682932034319</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.08742035038740836</v>
+        <v>-0.05654266249383377</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2857211456836861</v>
+        <v>0.1778094115055817</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.3012213710874782</v>
+        <v>0.2841727785903324</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.03157546173106818</v>
+        <v>0.09205165127481774</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.3330530399221047</v>
+        <v>-0.141473498967898</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.05775510723685248</v>
+        <v>0.3384165774052922</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.009244063411533276</v>
+        <v>-0.01797016691891817</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.09180075165453216</v>
+        <v>0.03773967510927467</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.333818543467101</v>
+        <v>0.1780372647039976</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.3190983490267625</v>
+        <v>-0.1190943561789405</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5674,58 +5675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.02956520551904285</v>
+        <v>0.006489908072392803</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.116039903241864</v>
+        <v>-0.01219162455757106</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3018832599149469</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1331205105803096</v>
+        <v>0.06968608946379998</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.414844741196839</v>
+        <v>0.1767676924371601</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3018832599149469</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.0164327516352607</v>
+        <v>0.0346244311529067</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.040189029865013</v>
+        <v>0.8606085575830302</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3018832599149469</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3900752392253577</v>
+        <v>0.2144494682959772</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1012713180234582</v>
+        <v>-0.04524932362007883</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.713491934457906</v>
+        <v>0.7883971018666882</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.02128572850164578</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.06378474174201731</v>
+        <v>0.01375357651872045</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.0203614049749441</v>
+        <v>0.03482458449137948</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0824670026783576</v>
+        <v>-0.02036191281927813</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5974,28 +5975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6004,10 +6005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6016,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6062,49 +6063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.09002986682938641</v>
+        <v>0.04823577932436307</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.02734435963470006</v>
+        <v>-0.05679722082872107</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1603957635724635</v>
+        <v>0.1234492339101719</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2069006720189944</v>
+        <v>0.4570755476210876</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2829863495851492</v>
+        <v>-0.315814243187495</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03889624361257016</v>
+        <v>-0.03605992585647466</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9133561795218198</v>
+        <v>1.088190551974653</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2829863495851492</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.5202358646850243</v>
+        <v>0.5320923724105275</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01111938179476002</v>
+        <v>-0.02151305410833948</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9681868521869144</v>
+        <v>0.9404630364375255</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1022317316320518</v>
+        <v>-0.06320652629413515</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6164,68 +6165,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.07378636095717539</v>
+        <v>-0.2448268083670267</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01203498633555444</v>
+        <v>-0.3204950001201411</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2622253758368088</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1497348611482323</v>
+        <v>0.2319077570512748</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1797026712816814</v>
+        <v>0.4060640797939929</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2207723013756367</v>
+        <v>-0.315814243187495</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1290394939501307</v>
+        <v>-0.03605992585647466</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7125564396455729</v>
+        <v>1.088190551974653</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2595355160283203</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3780135932703899</v>
+        <v>0.1037546223575094</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1036318997178892</v>
+        <v>-0.2950754739773539</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7035035755827982</v>
+        <v>0.1833842998814645</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07471818073633707</v>
+        <v>-0.06365726930468618</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01490189064218872</v>
+        <v>-0.2795769744477549</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.08676828979966644</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.09355276685575453</v>
+        <v>-0.2795769744477549</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.9069015013894919</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.4748825853361665</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6270,68 +6267,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05464882401835514</v>
+        <v>-0.03358824748837752</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.006001987906799067</v>
+        <v>-0.1304224977129982</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2622253758368087</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1483624000303649</v>
+        <v>0.1430849809775904</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1979857514979584</v>
+        <v>0.4500512888228594</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2570551024208101</v>
+        <v>-0.315814243187495</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.07646857609973301</v>
+        <v>-0.03605992585647466</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8296614540519247</v>
+        <v>1.088190551974653</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2595355160283203</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4195518772049187</v>
+        <v>0.4124990806794286</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.07661214255351512</v>
+        <v>-0.09789257069778534</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7808085503026149</v>
+        <v>0.7290841930057853</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.09340275911067686</v>
+        <v>-0.07905225979655861</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.03245878290834869</v>
+        <v>-0.07805879977258556</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.03616562550703994</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.06622918839042524</v>
+        <v>-0.07805879977258556</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.9069015013894919</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.1655269949776802</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6376,67 +6369,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3088639259249495</v>
+        <v>0.06783853323109112</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2335936956842988</v>
+        <v>-0.03915865865699886</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05838140064822201</v>
+        <v>0.01057158729636975</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1033489193909851</v>
+        <v>0.1158070972645086</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9064327485380117</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.07121848839623379</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3457311767825897</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.2298621349342879</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1254104153489787</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4092269382762355</v>
+        <v>0.06707208356503935</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08332829247992346</v>
+        <v>-0.3185031641068488</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7615932850758771</v>
+        <v>0.1185486179476764</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07471818073633718</v>
+        <v>-0.04992556603898313</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.2007596908625031</v>
+        <v>0.01870071055899558</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2953470426488958</v>
+        <v>0.462641195899576</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.073020857478447</v>
+        <v>-0.3035197467329241</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.05128529554140782</v>
+        <v>0.03723595092910825</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.04968647066593979</v>
+        <v>-0.03530206183892504</v>
       </c>
     </row>
     <row r="7">
@@ -6482,67 +6475,67 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1448569321946125</v>
+        <v>0.02815809595309493</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.07901842662345748</v>
+        <v>-0.07486312463454914</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.134682406219364</v>
+        <v>0.1150786202270108</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1793149283746856</v>
+        <v>0.4063627640122751</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2484463964898045</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.08894191220555525</v>
+        <v>0.00124772041103749</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8018763161069433</v>
+        <v>0.9969484920130616</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5233203950422964</v>
+        <v>0.4467529149236689</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.009112961371831707</v>
+        <v>-0.07601599833290129</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9739273286511628</v>
+        <v>0.7896271863530219</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07471818073633707</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05029868174594498</v>
+        <v>-0.01915378559603176</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.04817196029024085</v>
+        <v>0.03870328381218169</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.002028981442239175</v>
+        <v>-0.05570124819079236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="n">
-        <v>0.05128529554140782</v>
+        <v>0.03723595092910825</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.006526314267764954</v>
+        <v>-0.02072738717352474</v>
       </c>
     </row>
     <row r="8">
@@ -6588,68 +6581,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3367420067828579</v>
+        <v>-0.04799305312878777</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2598685620878403</v>
+        <v>-0.1433839449192882</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1037854592728726</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04136027603732909</v>
+        <v>0.08510994707029922</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.09993932957921133</v>
+        <v>0.1302067116140755</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6296296296296297</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.03397181375486624</v>
+        <v>-0.08742035038740836</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.3996986714733644</v>
+        <v>0.2857211456836861</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.1096461580852159</v>
+        <v>0.3012213710874782</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.08900501376493108</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.383750521792388</v>
+        <v>0.04320422581783223</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.0999001515364264</v>
+        <v>-0.3337466230866076</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7141803073192724</v>
+        <v>0.07636263834321998</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07471818073633718</v>
+        <v>-0.009244063411533276</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.2263352110443477</v>
+        <v>-0.09180075165453216</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3472939959876744</v>
+        <v>0.333818543467101</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.08977905735759928</v>
+        <v>-0.3190983490267626</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.04873520817013055</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6694,68 +6683,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1800763928270799</v>
+        <v>-0.01862566914458375</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.112212484264637</v>
+        <v>-0.1169591665085142</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.231288305099722</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.115776016655172</v>
+        <v>0.1310825508729322</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1763606768759317</v>
+        <v>0.4082968053646653</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.935672514619883</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2312883050997221</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1138026337307372</v>
+        <v>-0.0164327516352607</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7464975007580551</v>
+        <v>1.040189029865013</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.231288305099722</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5351352147441528</v>
+        <v>0.4057453066314571</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.001427676159082236</v>
+        <v>-0.1022059396959252</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9959153419213013</v>
+        <v>0.7171470272467775</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07471818073633718</v>
+        <v>-0.0790522597965585</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.08260922818529304</v>
+        <v>-0.06378474174201743</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.07210189716125437</v>
+        <v>0.0203614049749441</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.009800683173736058</v>
+        <v>-0.08246700267835771</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>0.007178166975881028</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6998,28 +6983,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1799741913752891</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450097</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7028,10 +7013,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.5373300241682992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7040,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7086,49 +7071,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02332536918041006</v>
+        <v>0.09002986682938641</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02097960988825964</v>
+        <v>0.02734435963470006</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1919673527633516</v>
+        <v>-0.2867967086275238</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09542986630280144</v>
+        <v>0.1603957635724635</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2710807151579593</v>
+        <v>0.2069006720189944</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1918863664962984</v>
+        <v>-0.2829863495851492</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04165366283465977</v>
+        <v>0.03889624361257016</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8558667097949493</v>
+        <v>0.9133561795218198</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1919673527633516</v>
+        <v>-0.2829863495851492</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2085857611200868</v>
+        <v>0.5202358646850243</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06012869244128138</v>
+        <v>-0.01111938179476002</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.729561694370469</v>
+        <v>0.9681868521869144</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04392141022055807</v>
+        <v>-0.1022317316320518</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7188,67 +7173,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.07378636095717539</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>0.01203498633555444</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2622253758368088</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.1497348611482323</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1797026712816814</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2207723013756367</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.1290394939501307</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.7125564396455729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2595355160283203</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3780135932703899</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.1036318997178892</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.7035035755827982</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.07471818073633707</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.03913486734061711</v>
+        <v>-0.01490189064218872</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2445033638472462</v>
+        <v>0.08676828979966644</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1650204430719699</v>
+        <v>-0.09355276685575453</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.2134223460531468</v>
+        <v>0.9069015013894919</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.1592570553973541</v>
+        <v>-0.4748825853361665</v>
       </c>
     </row>
     <row r="5">
@@ -7294,67 +7279,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>0.05464882401835514</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>-0.006001987906799067</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2622253758368087</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0.1483624000303649</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>0.1979857514979584</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2570551024208101</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.07646857609973301</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>0.8296614540519247</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.2595355160283203</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.4195518772049187</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.07661214255351512</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.7808085503026149</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.09340275911067686</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.04447864517159239</v>
+        <v>-0.03245878290834869</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.0878684466295574</v>
+        <v>0.03616562550703994</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1216572575582907</v>
+        <v>-0.06622918839042524</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.2134223460531468</v>
+        <v>0.9069015013894919</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1114588698733576</v>
+        <v>-0.1655269949776802</v>
       </c>
     </row>
     <row r="6">
@@ -7400,64 +7385,68 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02787440931566798</v>
+        <v>0.3088639259249495</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03034313930079358</v>
+        <v>0.2335936956842988</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04971417837815464</v>
+        <v>0.05838140064822201</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1212599950451121</v>
+        <v>0.1033489193909851</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.9064327485380117</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.06387704928419313</v>
+        <v>-0.07121848839623379</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2066569106734957</v>
+        <v>0.3457311767825897</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.2849094544886638</v>
+        <v>0.2298621349342879</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.09801218796067679</v>
+        <v>0.4092269382762355</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1461175664873063</v>
+        <v>-0.08332829247992346</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3428131313161925</v>
+        <v>0.7615932850758771</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02289602556240811</v>
+        <v>-0.07471818073633718</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05242255391963346</v>
+        <v>0.2007596908625031</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.158405095403602</v>
+        <v>0.2953470426488958</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.0914900511958151</v>
+        <v>-0.073020857478447</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.04968647066593979</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7502,64 +7491,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.02989700063240341</v>
+        <v>0.1448569321946125</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.02756702496466246</v>
+        <v>0.07901842662345748</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.09099260937618169</v>
+        <v>0.134682406219364</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2258051820804493</v>
+        <v>0.1793149283746856</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.2484463964898045</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.07720953785198659</v>
+        <v>0.08894191220555525</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7328334660509549</v>
+        <v>0.8018763161069433</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1608298545088545</v>
+        <v>0.5233203950422964</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.09726664974168286</v>
+        <v>-0.009112961371831707</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5625278567949983</v>
+        <v>0.9739273286511628</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.07471818073633707</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.006728578018330045</v>
+        <v>0.05029868174594498</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.03413406613534886</v>
+        <v>0.04817196029024085</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.03951387493343739</v>
+        <v>0.002028981442239175</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.006526314267764954</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7604,64 +7597,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.08141038848245086</v>
+        <v>0.3367420067828579</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.07920413672890436</v>
+        <v>0.2598685620878403</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1037854592728726</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1031106325266614</v>
+        <v>0.04136027603732909</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1421782585002016</v>
+        <v>0.09993932957921133</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1139317855593476</v>
+        <v>-0.03397181375486624</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1421366535938349</v>
+        <v>0.3996986714733644</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.508167538049784</v>
+        <v>0.1096461580852159</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.08900501376493108</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.0367030399543522</v>
+        <v>0.383750521792388</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1937953655775521</v>
+        <v>-0.0999001515364264</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.1283746880604574</v>
+        <v>0.7141803073192724</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.01232164979750494</v>
+        <v>-0.07471818073633718</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.05947223104719934</v>
+        <v>0.2263352110443477</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.09646487536532056</v>
+        <v>0.3472939959876744</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1422180590696667</v>
+        <v>-0.08977905735759928</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.04873520817013055</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7706,64 +7703,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1091436876433024</v>
+        <v>0.1800763928270799</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1070040452212114</v>
+        <v>0.112212484264637</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1847093048502678</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1241198546184887</v>
+        <v>0.115776016655172</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2362392793851624</v>
+        <v>0.1763606768759317</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.935672514619883</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1847093048502678</v>
+        <v>-0.2312883050997221</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.05090485257089106</v>
+        <v>0.1138026337307372</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8238550132417071</v>
+        <v>0.7464975007580551</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1847093048502678</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09268548955178169</v>
+        <v>0.5351352147441528</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1502599378105456</v>
+        <v>-0.001427676159082236</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3241821610345889</v>
+        <v>0.9959153419213013</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.07471818073633718</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.08786786894513343</v>
+        <v>0.08260922818529304</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.00888125301749132</v>
+        <v>0.07210189716125437</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.09589743259997674</v>
+        <v>0.009800683173736058</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0.007178166975881028</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7776,7 +7777,1015 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947869</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.02255028811919957</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.0273406545103132</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.0949279844316521</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2695420012099382</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1918863664962984</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.04165366283465977</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8558667097949493</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2095448849723227</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.06623537151227232</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.7094982221057377</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04392141022055807</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.0100920662696089</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.2963414873615395</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884719</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.03848492378498314</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.2445033638472462</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.165542694416976</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.2134223460531468</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1592570553973541</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.0633997631217984</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.06798993102723183</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.06596747922643247</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.214593190060595</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.13318215211393</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5391526104926985</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.1208786768201607</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.06538223130620624</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1775284606855828</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2213777581599597</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.04179189425919072</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.0878684466295574</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1191875187578634</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.2134223460531468</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1114588698733576</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.02869012210560173</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.02364863247405524</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.06793604487478933</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.04943721701214504</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.1205717642876783</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.9101123595505618</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.06387704928419313</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.2066569106734957</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.2849094544886638</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.06793604487478933</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.09888356152256872</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1516655451774558</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.3348099434878234</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.02289602556240811</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.05242255391963324</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.158405095403602</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.09149005119581499</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.02912713476458384</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.03388526880169851</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.164302162285406</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.0905377564896597</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2245267011508491</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.164302162285406</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.07720953785198659</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.7328334660509549</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.164302162285406</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.1617510796611477</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1031320302596039</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.5476731319804151</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.006728578018330156</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.03413406613534886</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.03951387493343717</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.08068140322119299</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.08518687583549356</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1267516996503394</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.1028882843395383</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.1413990745129039</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1139317855593476</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.1421366535938349</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.508167538049784</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1267516996503394</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.03752575907391575</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1990335646037054</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.1270585027624421</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.01232164979750494</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.05947223104719934</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.09646487536532056</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.1422180590696667</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.1084367113032002</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.1128061584080603</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1847093048502678</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.1239564990898047</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2349199210163277</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1847093048502678</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.05090485257089106</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.8238550132417071</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1847093048502678</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.09355263588904283</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1557810020369165</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.316759957396948</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04770980148098947</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.08786786894513343</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.00888125301749132</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.09589743259997674</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7882,24 +8891,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7930,20 +8937,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -7976,20 +8983,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8025,16 +9036,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -8064,24 +9073,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8112,21 +9119,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8143,37 +9152,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -8200,27 +9207,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8247,14 +9252,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8264,10 +9269,10 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8294,27 +9299,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8341,27 +9346,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -8388,27 +9393,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -8425,37 +9430,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8472,24 +9477,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8499,10 +9504,10 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8529,27 +9534,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8576,27 +9581,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8623,27 +9628,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -8670,14 +9675,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8687,7 +9692,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -8696,6 +9701,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
